--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:36</t>
+    <t xml:space="preserve">2026-09-12 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
@@ -36,18 +36,18 @@
     <t xml:space="preserve">Arica y Parinacota</t>
   </si>
   <si>
+    <t xml:space="preserve">Arica</t>
+  </si>
+  <si>
     <t xml:space="preserve">Putre</t>
   </si>
   <si>
-    <t xml:space="preserve">Arica</t>
+    <t xml:space="preserve">General Lagos</t>
   </si>
   <si>
     <t xml:space="preserve">Camarones</t>
   </si>
   <si>
-    <t xml:space="preserve">General Lagos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:52</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,13 +487,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>15201</v>
+        <v>15101</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.87</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="3">
@@ -504,13 +504,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>15101</v>
+        <v>15201</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-2.3</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="4">
@@ -521,13 +521,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15102</v>
+        <v>15202</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-18.26</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="5">
@@ -538,13 +538,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>15202</v>
+        <v>15102</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-28.75</v>
+        <v>-7.37</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.88</v>
+        <v>-8.76</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>-1.4</v>
+        <v>-14.01</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-5.46</v>
+        <v>-54.6</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-7.37</v>
+        <v>-73.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:34</t>
+    <t xml:space="preserve">2026-10-05 08:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
